--- a/nr-update-termino/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-update-termino/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T09:32:52+00:00</t>
+    <t>2025-07-21T12:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-termino/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/nr-update-termino/ig/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:02:52+00:00</t>
+    <t>2025-07-21T12:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
